--- a/Data/EXCEL/Transfer/salemon/202507-1/1623-salemon-202507.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202507-1/1623-salemon-202507.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202507\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{521C6475-AC1E-43EC-AF29-59B80C037B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{313E921A-8F95-4843-A475-9C9A378EB6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="585" windowWidth="21750" windowHeight="13170" xr2:uid="{892085CE-8948-4C25-A5CB-FBDF0EA393B3}"/>
+    <workbookView xWindow="6525" yWindow="930" windowWidth="21750" windowHeight="13170" xr2:uid="{BE9F3ABD-EF2C-44B8-BAF5-4C81887B667E}"/>
   </bookViews>
   <sheets>
     <sheet name="1623-salemon-202507" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -845,6 +845,9 @@
     <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -854,16 +857,13 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,8 +1258,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{235BA7A5-7F9A-459E-A24A-9F463DD6CAFC}">
-  <dimension ref="A1:Q18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F0E62B-3E57-46F3-AF10-510ADD2AECA9}">
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
@@ -1423,743 +1423,796 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
+        <v>45839</v>
+      </c>
+      <c r="B5" s="6">
+        <v>218</v>
+      </c>
+      <c r="C5" s="6">
+        <v>214.5</v>
+      </c>
+      <c r="D5" s="6">
+        <v>220</v>
+      </c>
+      <c r="E5" s="6">
+        <v>211</v>
+      </c>
+      <c r="F5" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="G5" s="7">
+        <v>-1.61</v>
+      </c>
+      <c r="H5" s="8">
+        <v>5.41</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1.94</v>
+      </c>
+      <c r="J5" s="9">
+        <v>22.1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>37.79</v>
+      </c>
+      <c r="L5" s="9">
+        <v>29.5</v>
+      </c>
+      <c r="M5" s="8">
+        <v>5.41</v>
+      </c>
+      <c r="N5" s="9">
+        <v>1.94</v>
+      </c>
+      <c r="O5" s="9">
+        <v>22.1</v>
+      </c>
+      <c r="P5" s="8">
+        <v>37.79</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
         <v>45809</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B6" s="12">
         <v>196.5</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C6" s="12">
         <v>218</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D6" s="12">
         <v>219</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E6" s="12">
         <v>195</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F6" s="13">
         <v>21.5</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G6" s="13">
         <v>10.94</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H6" s="14">
         <v>5.3</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I6" s="13">
         <v>0.25</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J6" s="13">
         <v>34.9</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K6" s="14">
         <v>32.39</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L6" s="13">
         <v>30.9</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M6" s="14">
         <v>5.3</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N6" s="13">
         <v>0.25</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O6" s="13">
         <v>34.9</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P6" s="14">
         <v>32.39</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q6" s="13">
         <v>30.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>45778</v>
-      </c>
-      <c r="B6" s="11">
-        <v>181</v>
-      </c>
-      <c r="C6" s="11">
-        <v>196.5</v>
-      </c>
-      <c r="D6" s="11">
-        <v>204.5</v>
-      </c>
-      <c r="E6" s="11">
-        <v>174.5</v>
-      </c>
-      <c r="F6" s="12">
-        <v>15.5</v>
-      </c>
-      <c r="G6" s="12">
-        <v>8.56</v>
-      </c>
-      <c r="H6" s="13">
-        <v>5.29</v>
-      </c>
-      <c r="I6" s="12">
-        <v>1.18</v>
-      </c>
-      <c r="J6" s="12">
-        <v>61.4</v>
-      </c>
-      <c r="K6" s="13">
-        <v>27.08</v>
-      </c>
-      <c r="L6" s="12">
-        <v>30.1</v>
-      </c>
-      <c r="M6" s="13">
-        <v>5.29</v>
-      </c>
-      <c r="N6" s="12">
-        <v>1.18</v>
-      </c>
-      <c r="O6" s="12">
-        <v>61.4</v>
-      </c>
-      <c r="P6" s="13">
-        <v>27.08</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>30.1</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
+        <v>45778</v>
+      </c>
+      <c r="B7" s="6">
+        <v>181</v>
+      </c>
+      <c r="C7" s="6">
+        <v>196.5</v>
+      </c>
+      <c r="D7" s="6">
+        <v>204.5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>174.5</v>
+      </c>
+      <c r="F7" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="G7" s="9">
+        <v>8.56</v>
+      </c>
+      <c r="H7" s="8">
+        <v>5.29</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1.18</v>
+      </c>
+      <c r="J7" s="9">
+        <v>61.4</v>
+      </c>
+      <c r="K7" s="8">
+        <v>27.08</v>
+      </c>
+      <c r="L7" s="9">
+        <v>30.1</v>
+      </c>
+      <c r="M7" s="8">
+        <v>5.29</v>
+      </c>
+      <c r="N7" s="9">
+        <v>1.18</v>
+      </c>
+      <c r="O7" s="9">
+        <v>61.4</v>
+      </c>
+      <c r="P7" s="8">
+        <v>27.08</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
         <v>45748</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B8" s="12">
         <v>195</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C8" s="12">
         <v>181</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D8" s="12">
         <v>199</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E8" s="12">
         <v>166.5</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F8" s="15">
         <v>-14</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G8" s="15">
         <v>-7.18</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H8" s="14">
         <v>5.23</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I8" s="15">
         <v>-12.8</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J8" s="13">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K8" s="14">
         <v>21.79</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L8" s="13">
         <v>24.3</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M8" s="14">
         <v>5.23</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N8" s="15">
         <v>-12.8</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O8" s="13">
         <v>0.14000000000000001</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P8" s="14">
         <v>21.79</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q8" s="13">
         <v>24.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>45717</v>
-      </c>
-      <c r="B8" s="11">
-        <v>224</v>
-      </c>
-      <c r="C8" s="11">
-        <v>195</v>
-      </c>
-      <c r="D8" s="11">
-        <v>224.5</v>
-      </c>
-      <c r="E8" s="11">
-        <v>175</v>
-      </c>
-      <c r="F8" s="15">
-        <v>-29</v>
-      </c>
-      <c r="G8" s="15">
-        <v>-12.95</v>
-      </c>
-      <c r="H8" s="13">
-        <v>5.99</v>
-      </c>
-      <c r="I8" s="12">
-        <v>13.8</v>
-      </c>
-      <c r="J8" s="12">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="K8" s="13">
-        <v>16.57</v>
-      </c>
-      <c r="L8" s="12">
-        <v>34.5</v>
-      </c>
-      <c r="M8" s="13">
-        <v>5.99</v>
-      </c>
-      <c r="N8" s="12">
-        <v>13.8</v>
-      </c>
-      <c r="O8" s="12">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="P8" s="13">
-        <v>16.57</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>34.5</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
+        <v>45717</v>
+      </c>
+      <c r="B9" s="6">
+        <v>224</v>
+      </c>
+      <c r="C9" s="6">
+        <v>195</v>
+      </c>
+      <c r="D9" s="6">
+        <v>224.5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>175</v>
+      </c>
+      <c r="F9" s="7">
+        <v>-29</v>
+      </c>
+      <c r="G9" s="7">
+        <v>-12.95</v>
+      </c>
+      <c r="H9" s="8">
+        <v>5.99</v>
+      </c>
+      <c r="I9" s="9">
+        <v>13.8</v>
+      </c>
+      <c r="J9" s="9">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="K9" s="8">
+        <v>16.57</v>
+      </c>
+      <c r="L9" s="9">
+        <v>34.5</v>
+      </c>
+      <c r="M9" s="8">
+        <v>5.99</v>
+      </c>
+      <c r="N9" s="9">
+        <v>13.8</v>
+      </c>
+      <c r="O9" s="9">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="P9" s="8">
+        <v>16.57</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
         <v>45689</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B10" s="12">
         <v>212</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="12">
         <v>224</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D10" s="12">
         <v>225</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E10" s="12">
         <v>209</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F10" s="13">
         <v>12</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G10" s="13">
         <v>5.66</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H10" s="14">
         <v>5.26</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I10" s="15">
         <v>-0.87</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J10" s="13">
         <v>24.6</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K10" s="14">
         <v>10.57</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L10" s="13">
         <v>31.2</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M10" s="14">
         <v>5.26</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N10" s="15">
         <v>-0.87</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O10" s="13">
         <v>24.6</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P10" s="14">
         <v>10.57</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q10" s="13">
         <v>31.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>45658</v>
-      </c>
-      <c r="B10" s="11">
-        <v>234.5</v>
-      </c>
-      <c r="C10" s="11">
-        <v>212</v>
-      </c>
-      <c r="D10" s="11">
-        <v>236.5</v>
-      </c>
-      <c r="E10" s="11">
-        <v>209</v>
-      </c>
-      <c r="F10" s="15">
-        <v>-22.5</v>
-      </c>
-      <c r="G10" s="15">
-        <v>-9.59</v>
-      </c>
-      <c r="H10" s="13">
-        <v>5.31</v>
-      </c>
-      <c r="I10" s="15">
-        <v>-1.71</v>
-      </c>
-      <c r="J10" s="12">
-        <v>38.4</v>
-      </c>
-      <c r="K10" s="13">
-        <v>5.31</v>
-      </c>
-      <c r="L10" s="12">
-        <v>38.4</v>
-      </c>
-      <c r="M10" s="13">
-        <v>5.31</v>
-      </c>
-      <c r="N10" s="15">
-        <v>-1.71</v>
-      </c>
-      <c r="O10" s="12">
-        <v>38.4</v>
-      </c>
-      <c r="P10" s="13">
-        <v>5.31</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>38.4</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
+        <v>45658</v>
+      </c>
+      <c r="B11" s="6">
+        <v>234.5</v>
+      </c>
+      <c r="C11" s="6">
+        <v>212</v>
+      </c>
+      <c r="D11" s="6">
+        <v>236.5</v>
+      </c>
+      <c r="E11" s="6">
+        <v>209</v>
+      </c>
+      <c r="F11" s="7">
+        <v>-22.5</v>
+      </c>
+      <c r="G11" s="7">
+        <v>-9.59</v>
+      </c>
+      <c r="H11" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="I11" s="7">
+        <v>-1.71</v>
+      </c>
+      <c r="J11" s="9">
+        <v>38.4</v>
+      </c>
+      <c r="K11" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="L11" s="9">
+        <v>38.4</v>
+      </c>
+      <c r="M11" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="N11" s="7">
+        <v>-1.71</v>
+      </c>
+      <c r="O11" s="9">
+        <v>38.4</v>
+      </c>
+      <c r="P11" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
         <v>45627</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B12" s="12">
         <v>250</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="12">
         <v>234.5</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D12" s="12">
         <v>250</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E12" s="12">
         <v>210</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F12" s="15">
         <v>-15.5</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G12" s="15">
         <v>-6.2</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H12" s="14">
         <v>5.4</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I12" s="13">
         <v>7.01</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J12" s="15">
         <v>-31.1</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K12" s="14">
         <v>54.28</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L12" s="13">
         <v>28.7</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M12" s="14">
         <v>5.4</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N12" s="13">
         <v>7.01</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O12" s="15">
         <v>-31.1</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P12" s="14">
         <v>54.28</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q12" s="13">
         <v>28.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>45597</v>
-      </c>
-      <c r="B12" s="11">
-        <v>240</v>
-      </c>
-      <c r="C12" s="11">
-        <v>250</v>
-      </c>
-      <c r="D12" s="11">
-        <v>250</v>
-      </c>
-      <c r="E12" s="11">
-        <v>237.5</v>
-      </c>
-      <c r="F12" s="12">
-        <v>10</v>
-      </c>
-      <c r="G12" s="12">
-        <v>4.17</v>
-      </c>
-      <c r="H12" s="13">
-        <v>5.05</v>
-      </c>
-      <c r="I12" s="12">
-        <v>7.92</v>
-      </c>
-      <c r="J12" s="12">
-        <v>123.1</v>
-      </c>
-      <c r="K12" s="13">
-        <v>48.88</v>
-      </c>
-      <c r="L12" s="12">
-        <v>42.4</v>
-      </c>
-      <c r="M12" s="13">
-        <v>5.05</v>
-      </c>
-      <c r="N12" s="12">
-        <v>7.92</v>
-      </c>
-      <c r="O12" s="12">
-        <v>123.1</v>
-      </c>
-      <c r="P12" s="13">
-        <v>48.88</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>42.4</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
+        <v>45597</v>
+      </c>
+      <c r="B13" s="6">
+        <v>240</v>
+      </c>
+      <c r="C13" s="6">
+        <v>250</v>
+      </c>
+      <c r="D13" s="6">
+        <v>250</v>
+      </c>
+      <c r="E13" s="6">
+        <v>237.5</v>
+      </c>
+      <c r="F13" s="9">
+        <v>10</v>
+      </c>
+      <c r="G13" s="9">
+        <v>4.17</v>
+      </c>
+      <c r="H13" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="I13" s="9">
+        <v>7.92</v>
+      </c>
+      <c r="J13" s="9">
+        <v>123.1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>48.88</v>
+      </c>
+      <c r="L13" s="9">
+        <v>42.4</v>
+      </c>
+      <c r="M13" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="N13" s="9">
+        <v>7.92</v>
+      </c>
+      <c r="O13" s="9">
+        <v>123.1</v>
+      </c>
+      <c r="P13" s="8">
+        <v>48.88</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
         <v>45566</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B14" s="12">
         <v>249.5</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C14" s="12">
         <v>240</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D14" s="12">
         <v>251</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E14" s="12">
         <v>228.5</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F14" s="15">
         <v>-9.5</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G14" s="15">
         <v>-3.81</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H14" s="14">
         <v>4.68</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I14" s="13">
         <v>34.9</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J14" s="13">
         <v>219.5</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K14" s="14">
         <v>43.83</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L14" s="13">
         <v>36.700000000000003</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M14" s="14">
         <v>4.68</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N14" s="13">
         <v>34.9</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O14" s="13">
         <v>219.5</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P14" s="14">
         <v>43.83</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="Q14" s="13">
         <v>36.700000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>45536</v>
-      </c>
-      <c r="B14" s="11">
-        <v>239</v>
-      </c>
-      <c r="C14" s="11">
-        <v>249.5</v>
-      </c>
-      <c r="D14" s="11">
-        <v>254</v>
-      </c>
-      <c r="E14" s="11">
-        <v>224.5</v>
-      </c>
-      <c r="F14" s="12">
-        <v>10.5</v>
-      </c>
-      <c r="G14" s="12">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="H14" s="13">
-        <v>3.47</v>
-      </c>
-      <c r="I14" s="15">
-        <v>-46.7</v>
-      </c>
-      <c r="J14" s="12">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="K14" s="13">
-        <v>39.15</v>
-      </c>
-      <c r="L14" s="12">
-        <v>28</v>
-      </c>
-      <c r="M14" s="13">
-        <v>3.47</v>
-      </c>
-      <c r="N14" s="15">
-        <v>-46.7</v>
-      </c>
-      <c r="O14" s="12">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="P14" s="13">
-        <v>39.15</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
+        <v>45536</v>
+      </c>
+      <c r="B15" s="6">
+        <v>239</v>
+      </c>
+      <c r="C15" s="6">
+        <v>249.5</v>
+      </c>
+      <c r="D15" s="6">
+        <v>254</v>
+      </c>
+      <c r="E15" s="6">
+        <v>224.5</v>
+      </c>
+      <c r="F15" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="H15" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="I15" s="7">
+        <v>-46.7</v>
+      </c>
+      <c r="J15" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="K15" s="8">
+        <v>39.15</v>
+      </c>
+      <c r="L15" s="9">
+        <v>28</v>
+      </c>
+      <c r="M15" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="N15" s="7">
+        <v>-46.7</v>
+      </c>
+      <c r="O15" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="P15" s="8">
+        <v>39.15</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
         <v>45505</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B16" s="12">
         <v>241</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C16" s="12">
         <v>239</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D16" s="12">
         <v>247</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E16" s="12">
         <v>204</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F16" s="15">
         <v>-2</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G16" s="15">
         <v>-0.83</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H16" s="14">
         <v>6.51</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I16" s="13">
         <v>47</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J16" s="13">
         <v>56.5</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K16" s="14">
         <v>35.68</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L16" s="13">
         <v>28.8</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M16" s="14">
         <v>6.51</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N16" s="13">
         <v>47</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O16" s="13">
         <v>56.5</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P16" s="14">
         <v>35.68</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q16" s="13">
         <v>28.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>45474</v>
-      </c>
-      <c r="B16" s="11">
-        <v>209</v>
-      </c>
-      <c r="C16" s="11">
-        <v>241</v>
-      </c>
-      <c r="D16" s="11">
-        <v>266</v>
-      </c>
-      <c r="E16" s="11">
-        <v>205</v>
-      </c>
-      <c r="F16" s="12">
-        <v>32</v>
-      </c>
-      <c r="G16" s="12">
-        <v>15.31</v>
-      </c>
-      <c r="H16" s="13">
-        <v>4.43</v>
-      </c>
-      <c r="I16" s="12">
-        <v>12.5</v>
-      </c>
-      <c r="J16" s="12">
-        <v>25.3</v>
-      </c>
-      <c r="K16" s="13">
-        <v>29.18</v>
-      </c>
-      <c r="L16" s="12">
-        <v>31.4</v>
-      </c>
-      <c r="M16" s="13">
-        <v>4.43</v>
-      </c>
-      <c r="N16" s="12">
-        <v>12.5</v>
-      </c>
-      <c r="O16" s="12">
-        <v>25.3</v>
-      </c>
-      <c r="P16" s="13">
-        <v>29.18</v>
-      </c>
-      <c r="Q16" s="12">
-        <v>31.4</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
+        <v>45474</v>
+      </c>
+      <c r="B17" s="6">
+        <v>209</v>
+      </c>
+      <c r="C17" s="6">
+        <v>241</v>
+      </c>
+      <c r="D17" s="6">
+        <v>266</v>
+      </c>
+      <c r="E17" s="6">
+        <v>205</v>
+      </c>
+      <c r="F17" s="9">
+        <v>32</v>
+      </c>
+      <c r="G17" s="9">
+        <v>15.31</v>
+      </c>
+      <c r="H17" s="8">
+        <v>4.43</v>
+      </c>
+      <c r="I17" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="J17" s="9">
+        <v>25.3</v>
+      </c>
+      <c r="K17" s="8">
+        <v>29.18</v>
+      </c>
+      <c r="L17" s="9">
+        <v>31.4</v>
+      </c>
+      <c r="M17" s="8">
+        <v>4.43</v>
+      </c>
+      <c r="N17" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="O17" s="9">
+        <v>25.3</v>
+      </c>
+      <c r="P17" s="8">
+        <v>29.18</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
         <v>45444</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B18" s="12">
         <v>214.5</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="12">
         <v>209</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D18" s="12">
         <v>237.5</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E18" s="12">
         <v>196</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F18" s="15">
         <v>-5.5</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G18" s="15">
         <v>-2.56</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H18" s="14">
         <v>3.93</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I18" s="13">
         <v>19.899999999999999</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J18" s="13">
         <v>49.9</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K18" s="14">
         <v>24.75</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L18" s="13">
         <v>21.5</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M18" s="14">
         <v>3.93</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N18" s="13">
         <v>19.899999999999999</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O18" s="13">
         <v>49.9</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P18" s="14">
         <v>24.75</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q18" s="13">
         <v>21.5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>45413</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B19" s="6">
         <v>212.5</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C19" s="6">
         <v>214.5</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D19" s="6">
         <v>306</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E19" s="6">
         <v>107</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F19" s="9">
         <v>2</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G19" s="9">
         <v>0.94</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H19" s="8">
         <v>3.28</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J19" s="9">
         <v>42</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K19" s="8">
         <v>20.82</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L19" s="9">
         <v>29.7</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M19" s="8">
         <v>3.28</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="N19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O19" s="9">
         <v>42</v>
       </c>
-      <c r="P18" s="13">
+      <c r="P19" s="8">
         <v>20.82</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q19" s="9">
         <v>29.7</v>
       </c>
     </row>
